--- a/jogos_2024-12-13.xlsx
+++ b/jogos_2024-12-13.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
         <v>3.4</v>
       </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.09</v>
-      </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>3.2</v>
+        <v>2.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.35</v>
+        <v>6.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['38', '44', '46']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI4" t="n">
         <v>2</v>
       </c>
-      <c r="AD4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['53', '65']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45639.375</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['53', '65']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['38', '44', '46']</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.42</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45639.375</v>
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z7" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['26', '38', '77', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45639.41666666666</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
         <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -1476,50 +1476,50 @@
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Z8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['25', '75']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45639.41666666666</v>
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.25</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['26', '38', '77', '82']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>2.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['25', '75']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45639.41666666666</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,80 +1701,80 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
         <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.33</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="AC10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.63</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.4</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.62</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.63</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1893,17 +1893,17 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.62</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
         <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
         <v>1.53</v>
@@ -2499,59 +2499,59 @@
         <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['42', '74']</t>
+          <t>['90+7']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45639.5</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O17" t="n">
         <v>3.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.38</v>
       </c>
       <c r="P17" t="n">
         <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
         <v>1.53</v>
@@ -2628,59 +2628,59 @@
         <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['90+7']</t>
+          <t>['42', '74']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45639.5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ankaragücü</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>3.83</v>
+        <v>3.59</v>
       </c>
       <c r="N20" t="n">
-        <v>5.06</v>
+        <v>3.17</v>
       </c>
       <c r="O20" t="n">
-        <v>2.13</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="U20" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>3.44</v>
+        <v>4.12</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>['57', '82']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45639.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yeni Malatyaspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['63', '65', '75']</t>
+          <t>['67', '82']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45639.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Ankaragücü</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="O22" t="n">
         <v>2.13</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.63</v>
-      </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>4.12</v>
+        <v>3.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['57', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45639.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,16 +3352,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Yeni Malatyaspor</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['67', '82']</t>
+          <t>['63', '65', '75']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45639.58333333334</v>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
         <v>2</v>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="U24" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
         <v>1.17</v>
       </c>
       <c r="X24" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['45+2', '56', '62', '86']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['57', '87']</t>
+          <t>['19', '49']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45639.60416666666</v>
@@ -3739,16 +3739,16 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -3757,7 +3757,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q26" t="n">
         <v>4.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>6</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T26" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
         <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['57', '87']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['45+2', '56', '62', '86']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['19', '49']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AI26" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45639.60416666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,16 +4126,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>FC Schaffhausen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nîmes</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>2.27</v>
+        <v>3.26</v>
       </c>
       <c r="T29" t="n">
-        <v>3.62</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="X29" t="n">
-        <v>2.37</v>
+        <v>4.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="Z29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45639.64583333334</v>
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="O30" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="X30" t="n">
-        <v>2.95</v>
+        <v>2.37</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45639.64583333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Schaffhausen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>3.26</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA31" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45639.64583333334</v>
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
+      <c r="P33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T33" t="n">
         <v>3.2</v>
       </c>
-      <c r="M33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="U33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y33" t="n">
         <v>2.3</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="Z33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.28</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AH33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['62', '84']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['6', '9', '43', '48', '67', '90+1', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45639.64583333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O35" t="n">
         <v>3.1</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
       <c r="P35" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R35" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.32</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AI35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45639.64583333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,80 +5055,80 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="N36" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3.1</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.88</v>
-      </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S36" t="n">
-        <v>3.12</v>
+        <v>2.35</v>
       </c>
       <c r="T36" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y36" t="n">
         <v>2.5</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['62', '84']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['6', '9', '43', '48', '67', '90+1', '90+4']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AJ36" t="n">
         <v>1.8</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,16 +5158,16 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.87</v>
+        <v>1.83</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="T37" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="V37" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['50', '72', '86']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI37" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45639.66666666666</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P38" t="n">
         <v>2.4</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T38" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X38" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AD38" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5376,20 +5376,20 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '89']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AI38" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45639.66666666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.85</v>
+        <v>2.93</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="N39" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="O39" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA39" t="n">
         <v>4</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AC39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['13', '88', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45639.66666666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U41" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V41" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="X41" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['32', '44', '69']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45639.66666666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.05</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['6', '85', '89']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG42" t="n">
         <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45639.66666666666</v>
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="P43" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="R43" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T43" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
         <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['56', '60']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45639.66666666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.93</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>2.84</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="P44" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['13', '88', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45639.66666666666</v>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,49 +6216,49 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="O45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S45" t="n">
         <v>2.4</v>
       </c>
-      <c r="P45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W45" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X45" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA45" t="n">
         <v>4.33</v>
@@ -6267,32 +6267,32 @@
         <v>1.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['50', '72', '86']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AH45" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45639.66666666666</v>
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="M46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q46" t="n">
         <v>4.5</v>
       </c>
-      <c r="N46" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T46" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q46" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
         <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['56', '60']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI46" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ46" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45639.66666666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,91 +6448,91 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X47" t="n">
         <v>4</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N47" t="n">
-        <v>5</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>6</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.3</v>
-      </c>
       <c r="Y47" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC47" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['20', '47', '72', '76']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45639.66666666666</v>
@@ -6577,87 +6577,87 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>2</v>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>2.25</v>
-      </c>
       <c r="M48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S48" t="n">
         <v>4</v>
       </c>
-      <c r="N48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="U48" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X48" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6666,20 +6666,20 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['24', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AI48" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45639.66666666666</v>
@@ -6835,16 +6835,16 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X50" t="n">
         <v>4.5</v>
       </c>
-      <c r="N50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="Y50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD50" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '80']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>2</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45639.66666666666</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N51" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="P51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z51" t="n">
         <v>2.5</v>
       </c>
-      <c r="U51" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X51" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2</v>
-      </c>
       <c r="AA51" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.68</v>
+        <v>2.88</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45639.66666666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q52" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="T52" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U52" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W52" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="X52" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="Y52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z52" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>['54', '80']</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AI52" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45639.66666666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
         <v>3</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD53" t="n">
         <v>1.75</v>
       </c>
-      <c r="M53" t="n">
-        <v>4</v>
-      </c>
-      <c r="N53" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O53" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T53" t="n">
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['6', '85', '89']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>2.45</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['32', '44', '69']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>2.62</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45639.66666666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,19 +7351,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O54" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S54" t="n">
         <v>2.5</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U54" t="n">
         <v>1.3</v>
       </c>
-      <c r="S54" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.55</v>
-      </c>
       <c r="V54" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.2</v>
       </c>
-      <c r="X54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC54" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45639.66666666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,16 +7480,16 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -7506,65 +7506,65 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N55" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="P55" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="R55" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S55" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="T55" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W55" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X55" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['20', '47', '72', '76']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -7573,16 +7573,16 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45639.66666666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,22 +7867,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="M58" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="O58" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P58" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="S58" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="T58" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="U58" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V58" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W58" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X58" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
         <v>1.53</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC58" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['49', '68']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AI58" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45639.6875</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,19 +7996,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
         <v>2</v>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="N59" t="n">
-        <v>5.75</v>
+        <v>3.64</v>
       </c>
       <c r="O59" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="P59" t="n">
         <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R59" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S59" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U59" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V59" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W59" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X59" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Z59" t="n">
         <v>1.6</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['5', '40', '68']</t>
+          <t>['19', '45+1']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '68']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.11</v>
+        <v>1.58</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45639.6875</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,19 +8254,19 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>2</v>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>3.64</v>
+        <v>5.75</v>
       </c>
       <c r="O61" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="R61" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S61" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T61" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V61" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W61" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X61" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Z61" t="n">
         <v>1.6</v>
       </c>
       <c r="AA61" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['19', '45+1']</t>
+          <t>['5', '40', '68']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['53', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.58</v>
+        <v>2.11</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45639.6875</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,109 +8383,109 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G62" t="n">
         <v>1</v>
       </c>
       <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X62" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y62" t="n">
         <v>3</v>
       </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="M62" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O62" t="n">
-        <v>5</v>
-      </c>
-      <c r="P62" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S62" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T62" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W62" t="n">
+      <c r="Z62" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD62" t="n">
         <v>1.5</v>
       </c>
-      <c r="X62" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>['24', '47', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="AI62" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45639.6875</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,19 +8512,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O63" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M63" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N63" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2.75</v>
       </c>
       <c r="P63" t="n">
         <v>2.2</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="R63" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T63" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U63" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V63" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W63" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X63" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="Y63" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD63" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['42', '51', '61']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['75', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45639.6875</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,25 +8641,25 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
       <c r="M64" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O64" t="n">
+        <v>5</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['24', '47', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI64" t="n">
         <v>3.1</v>
       </c>
-      <c r="P64" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T64" t="n">
-        <v>4</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ64" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45639.6875</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,22 +8770,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="n">
         <v>2</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N65" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O65" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P65" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q65" t="n">
         <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S65" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="T65" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U65" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V65" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W65" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X65" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['49', '68']</t>
+          <t>['42', '51', '61']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75', '83']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI65" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI65" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ65" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45639.6875</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,19 +8899,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="N66" t="n">
-        <v>5.75</v>
+        <v>2.63</v>
       </c>
       <c r="O66" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="P66" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="R66" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="S66" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="T66" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="U66" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="V66" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W66" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="X66" t="n">
-        <v>3.45</v>
+        <v>2.37</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AA66" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AC66" t="n">
         <v>2</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AH66" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AJ66" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45639.6875</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,16 +9028,16 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.62</v>
+        <v>1.48</v>
       </c>
       <c r="M67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N67" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X67" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA67" t="n">
         <v>3</v>
       </c>
-      <c r="N67" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O67" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>4</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T67" t="n">
-        <v>4</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X67" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Z67" t="n">
+      <c r="AB67" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA67" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC67" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '85']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.52</v>
+        <v>2.7</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AJ67" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45639.69791666666</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,16 +9157,16 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -9175,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -9186,80 +9186,80 @@
         <v>2.62</v>
       </c>
       <c r="M68" t="n">
+        <v>3</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O68" t="n">
         <v>3.4</v>
       </c>
-      <c r="N68" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O68" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P68" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC68" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q68" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T68" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X68" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AD68" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AH68" t="n">
         <v>1.52</v>
       </c>
       <c r="AI68" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45639.69791666666</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,16 +9415,16 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -9441,83 +9441,83 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="M70" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="P70" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R70" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S70" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T70" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U70" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V70" t="n">
         <v>1.03</v>
       </c>
       <c r="W70" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X70" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z70" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI70" t="n">
         <v>2</v>
       </c>
-      <c r="AA70" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>['55', '85']</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG70" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ70" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45639.69791666666</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,22 +9673,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -9699,65 +9699,65 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.34</v>
+        <v>1.91</v>
       </c>
       <c r="M72" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="N72" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="O72" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="P72" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X72" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y72" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q72" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T72" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X72" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z72" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA72" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['8', '23', '29', '65']</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -9766,16 +9766,16 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="AI72" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ72" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45639.70833333334</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,109 +9802,109 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N73" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O73" t="n">
         <v>4</v>
       </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M73" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N73" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O73" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P73" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R73" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S73" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T73" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U73" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X73" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH73" t="n">
         <v>1.36</v>
       </c>
-      <c r="V73" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W73" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X73" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z73" t="n">
+      <c r="AI73" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ73" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>['8', '23', '29', '65']</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG73" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45639.70833333334</v>
@@ -10060,19 +10060,19 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -10086,83 +10086,83 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="M75" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N75" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R75" t="n">
         <v>1.57</v>
       </c>
-      <c r="O75" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P75" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q75" t="n">
+      <c r="S75" t="n">
         <v>2.25</v>
       </c>
-      <c r="R75" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S75" t="n">
-        <v>2.2</v>
-      </c>
       <c r="T75" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U75" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V75" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W75" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X75" t="n">
         <v>2.37</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA75" t="n">
-        <v>5.38</v>
+        <v>4.87</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>['4', '58', '69']</t>
+          <t>['12', '71']</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>['7', '47', '60']</t>
+          <t>['7', '48']</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.19</v>
+        <v>1.7</v>
       </c>
       <c r="AI75" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="AJ75" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>45639.79166666666</v>
@@ -10189,109 +10189,109 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G76" t="n">
+        <v>3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O76" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P76" t="n">
         <v>2</v>
       </c>
-      <c r="H76" t="n">
-        <v>2</v>
-      </c>
-      <c r="I76" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M76" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O76" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Q76" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R76" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S76" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T76" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U76" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V76" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W76" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X76" t="n">
         <v>2.37</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA76" t="n">
-        <v>4.87</v>
+        <v>5.38</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['12', '71']</t>
+          <t>['4', '58', '69']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>['7', '48']</t>
+          <t>['7', '47', '60']</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.28</v>
+        <v>1.98</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45639.79166666666</v>
@@ -10318,16 +10318,16 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
@@ -10344,22 +10344,22 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="M77" t="n">
         <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P77" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="R77" t="n">
         <v>1.67</v>
@@ -10380,13 +10380,13 @@
         <v>1.6</v>
       </c>
       <c r="X77" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Y77" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AA77" t="n">
         <v>6.28</v>
@@ -10395,32 +10395,32 @@
         <v>1.11</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AJ77" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45639.88541666666</v>
@@ -10447,16 +10447,16 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -10473,22 +10473,22 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="M78" t="n">
         <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="O78" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P78" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q78" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="R78" t="n">
         <v>1.67</v>
@@ -10509,13 +10509,13 @@
         <v>1.6</v>
       </c>
       <c r="X78" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AA78" t="n">
         <v>6.28</v>
@@ -10524,32 +10524,32 @@
         <v>1.11</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AJ78" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45639.88541666666</v>
